--- a/data/data_monitoreo_la_villa_letira_becara.xlsx
+++ b/data/data_monitoreo_la_villa_letira_becara.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,97 +447,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>204</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANCAYAN FIESTA DILVER HUMBERTO</t>
+          <t>PINTADO CHASQUERO ESTEFANY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
+          <t>BANCAYAN FIESTA DILVER HUMBERTO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LLENQUE ANTON HELEN JOHANA</t>
+          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>175</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>LLENQUE ANTON HELEN JOHANA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GONZALES FIESTAS MARIA MARIBEL</t>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PINTADO CHASQUERO ESTEFANY</t>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
+          <t>GONZALES FIESTAS MARIA MARIBEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANTON INGA FATIMA DEL ROSARIO</t>
+          <t>VELASCO PEÑA KAREN ARELLYS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VELASCO PEÑA KAREN ARELLYS</t>
+          <t>ANTON INGA FATIMA DEL ROSARIO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -547,17 +547,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>152</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -597,16 +597,26 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>CARRERA CARRASCO DEIVID FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>PINTADO BENITES CRISTOBAL RODRIGO</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/data_monitoreo_la_villa_letira_becara.xlsx
+++ b/data/data_monitoreo_la_villa_letira_becara.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6">
@@ -487,63 +487,63 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>VELASCO PEÑA KAREN ARELLYS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GONZALES FIESTAS MARIA MARIBEL</t>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VELASCO PEÑA KAREN ARELLYS</t>
+          <t>GONZALES FIESTAS MARIA MARIBEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANTON INGA FATIMA DEL ROSARIO</t>
+          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
+          <t>ANTON INGA FATIMA DEL ROSARIO</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -553,11 +553,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
+          <t>HERNANDEZ CARNERO ARTURO SEBASTIAN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">

--- a/data/data_monitoreo_la_villa_letira_becara.xlsx
+++ b/data/data_monitoreo_la_villa_letira_becara.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
@@ -483,21 +483,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LLENQUE ANTON HELEN JOHANA</t>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>LLENQUE ANTON HELEN JOHANA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8">
@@ -507,17 +507,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">

--- a/data/data_monitoreo_la_villa_letira_becara.xlsx
+++ b/data/data_monitoreo_la_villa_letira_becara.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
@@ -457,37 +457,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANCAYAN FIESTA DILVER HUMBERTO</t>
+          <t>MONDRAGON NONAJULCA MARISOL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
+          <t>BANCAYAN FIESTA DILVER HUMBERTO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEMOCHE ECHE URSULA YESSENIA</t>
+          <t>FABIANA REBECA ARRUNATEGUI SILUPU</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
@@ -497,27 +497,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VELASCO PEÑA KAREN ARELLYS</t>
+          <t>TEMOCHE ECHE URSULA YESSENIA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MONDRAGON NONAJULCA MARISOL</t>
+          <t>VELASCO PEÑA KAREN ARELLYS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -527,23 +527,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
+          <t>ANTON INGA FATIMA DEL ROSARIO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANTON INGA FATIMA DEL ROSARIO</t>
+          <t>BAUTISTA CHAVESTA ERICKA MEDALIT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">

--- a/data/data_monitoreo_la_villa_letira_becara.xlsx
+++ b/data/data_monitoreo_la_villa_letira_becara.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
